--- a/frontend/tests/e2e/fixtures/organisations.xlsx
+++ b/frontend/tests/e2e/fixtures/organisations.xlsx
@@ -1,46 +1,254 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aniket/Documents/Development/TradeDocs/frontend/tests/e2e/fixtures/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F56E6B8B-EE2F-F44B-89EE-13547C969733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="38400" yWindow="600" windowWidth="38400" windowHeight="21000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Organisations" sheetId="1" r:id="rId1"/>
     <sheet name="Addresses" sheetId="2" r:id="rId2"/>
     <sheet name="Instructions" sheetId="3" r:id="rId3"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="61">
+  <si>
+    <t>Organisation Name</t>
+  </si>
+  <si>
+    <t>Organisation Type</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Exporter</t>
+  </si>
+  <si>
+    <t>Consignee</t>
+  </si>
+  <si>
+    <t>Buyer</t>
+  </si>
+  <si>
+    <t>Notify Party</t>
+  </si>
+  <si>
+    <t>Vendor</t>
+  </si>
+  <si>
+    <t>Address Type</t>
+  </si>
+  <si>
+    <t>Address Line 1</t>
+  </si>
+  <si>
+    <t>Address Line 2</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>State / Province</t>
+  </si>
+  <si>
+    <t>PIN / ZIP</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Contact Name</t>
+  </si>
+  <si>
+    <t>Phone Dial Code</t>
+  </si>
+  <si>
+    <t>Phone Number</t>
+  </si>
+  <si>
+    <t>IEC Code</t>
+  </si>
+  <si>
+    <t>Tax Type</t>
+  </si>
+  <si>
+    <t>Tax Code</t>
+  </si>
+  <si>
+    <t>Registered</t>
+  </si>
+  <si>
+    <t>How to use this file</t>
+  </si>
+  <si>
+    <t>1. "Organisations" sheet — one row per organisation. Fill in the Organisation Name column for each of the 5 pre-listed types (leave Organisation Type as-is).</t>
+  </si>
+  <si>
+    <t>2. "Addresses" sheet — one row per address. The Organisation Name here must be typed EXACTLY the same as the matching row in the Organisations sheet (copy-paste it to be safe).</t>
+  </si>
+  <si>
+    <t>3. Every organisation needs at least one address. To add more addresses to the same organisation, add another row in the Addresses sheet with the same Organisation Name.</t>
+  </si>
+  <si>
+    <t>4. Address Type must be one of: Registered, Factory, Corporate Office, Delivery.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - Only ONE Registered / Factory / Corporate Office address is allowed per organisation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - You CAN add multiple Delivery addresses for the same organisation.</t>
+  </si>
+  <si>
+    <t>5. Country must be typed exactly as it appears in the app (e.g. "India", "United States") — it is used to search a dropdown.</t>
+  </si>
+  <si>
+    <t>6. Phone Dial Code can be left blank — the app auto-fills it based on the Country you pick, unless you want a different one.</t>
+  </si>
+  <si>
+    <t>7. Required fields (per address): Address Type, Address Line 1, City, Country. Everything else is optional.</t>
+  </si>
+  <si>
+    <t>When you are done, save this file and hand it back — the automated script reads it directly by these exact sheet names and column order, so please don't rename sheets, reorder columns, or add extra columns.</t>
+  </si>
+  <si>
+    <t>ExporterTest</t>
+  </si>
+  <si>
+    <t>ConsigneeTest</t>
+  </si>
+  <si>
+    <t>BuyerTest</t>
+  </si>
+  <si>
+    <t>Notify PartyTest</t>
+  </si>
+  <si>
+    <t>VendorTest</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Pakistan</t>
+  </si>
+  <si>
+    <t>Afganistan</t>
+  </si>
+  <si>
+    <t>United Arab Emirates</t>
+  </si>
+  <si>
+    <t>Kenya</t>
+  </si>
+  <si>
+    <t>Factory</t>
+  </si>
+  <si>
+    <t>Corporate Office</t>
+  </si>
+  <si>
+    <t>9876500001</t>
+  </si>
+  <si>
+    <t>3001600001</t>
+  </si>
+  <si>
+    <t>701700001</t>
+  </si>
+  <si>
+    <t>41800001</t>
+  </si>
+  <si>
+    <t>7001900001</t>
+  </si>
+  <si>
+    <t>9876500002</t>
+  </si>
+  <si>
+    <t>3001500002</t>
+  </si>
+  <si>
+    <t>701500002</t>
+  </si>
+  <si>
+    <t>41500002</t>
+  </si>
+  <si>
+    <t>7001500002</t>
+  </si>
+  <si>
+    <t>9876500003</t>
+  </si>
+  <si>
+    <t>3001600003</t>
+  </si>
+  <si>
+    <t>701700003</t>
+  </si>
+  <si>
+    <t>41800003</t>
+  </si>
+  <si>
+    <t>7001900003</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -63,17 +271,30 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -398,429 +619,977 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Organisation Name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Organisation Type</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v/>
-      </c>
-      <c r="B2" t="str">
-        <v>Exporter</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v/>
-      </c>
-      <c r="B3" t="str">
-        <v>Consignee</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v/>
-      </c>
-      <c r="B4" t="str">
-        <v>Buyer</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v/>
-      </c>
-      <c r="B5" t="str">
-        <v>Notify Party</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v/>
-      </c>
-      <c r="B6" t="str">
-        <v>Vendor</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B6"/>
+    <ignoredError sqref="A1:B1 B2:B6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:O25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="32" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="34.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="36.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="38.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="37.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="31.83203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="32" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="32.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Organisation Name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Address Type</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Address Line 1</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Address Line 2</v>
-      </c>
-      <c r="E1" t="str">
-        <v>City</v>
-      </c>
-      <c r="F1" t="str">
-        <v>State / Province</v>
-      </c>
-      <c r="G1" t="str">
-        <v>PIN / ZIP</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Country</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Email</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Contact Name</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Phone Dial Code</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Phone Number</v>
-      </c>
-      <c r="M1" t="str">
-        <v>IEC Code</v>
-      </c>
-      <c r="N1" t="str">
-        <v>Tax Type</v>
-      </c>
-      <c r="O1" t="str">
-        <v>Tax Code</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v/>
-      </c>
-      <c r="B2" t="str">
-        <v>Registered</v>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
       </c>
       <c r="C2" t="str">
-        <v/>
+        <f>$A2&amp;" "&amp; $B2&amp;" "&amp;C$1</f>
+        <v>ExporterTest Registered Address Line 1</v>
       </c>
       <c r="D2" t="str">
-        <v/>
+        <f t="shared" ref="D2:O2" si="0">$A2&amp;" "&amp; $B2&amp;" "&amp;D$1</f>
+        <v>ExporterTest Registered Address Line 2</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <f t="shared" si="0"/>
+        <v>ExporterTest Registered City</v>
       </c>
       <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
-      <c r="H2" t="str">
-        <v/>
+        <f t="shared" si="0"/>
+        <v>ExporterTest Registered State / Province</v>
+      </c>
+      <c r="G2">
+        <v>500001</v>
+      </c>
+      <c r="H2" t="s">
+        <v>39</v>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <f>$A2&amp;" "&amp; $B2&amp;"@gmail.com"</f>
+        <v>ExporterTest Registered@gmail.com</v>
       </c>
       <c r="J2" t="str">
-        <v/>
-      </c>
-      <c r="K2" t="str">
-        <v/>
-      </c>
-      <c r="L2" t="str">
-        <v/>
-      </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v/>
-      </c>
-      <c r="B3" t="str">
-        <v>Registered</v>
+        <f t="shared" si="0"/>
+        <v>ExporterTest Registered Contact Name</v>
+      </c>
+      <c r="K2">
+        <v>91</v>
+      </c>
+      <c r="L2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M2">
+        <v>500001</v>
+      </c>
+      <c r="N2" s="3"/>
+      <c r="O2">
+        <f>LEN(N2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
       </c>
       <c r="C3" t="str">
-        <v/>
+        <f t="shared" ref="C3:O16" si="1">$A3&amp;" "&amp; $B3&amp;" "&amp;C$1</f>
+        <v>ConsigneeTest Registered Address Line 1</v>
       </c>
       <c r="D3" t="str">
-        <v/>
+        <f t="shared" si="1"/>
+        <v>ConsigneeTest Registered Address Line 2</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <f t="shared" si="1"/>
+        <v>ConsigneeTest Registered City</v>
       </c>
       <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
+        <f t="shared" si="1"/>
+        <v>ConsigneeTest Registered State / Province</v>
+      </c>
+      <c r="G3">
+        <v>600001</v>
+      </c>
+      <c r="H3" t="s">
+        <v>40</v>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <f t="shared" ref="I3:I16" si="2">$A3&amp;" "&amp; $B3&amp;"@gmail.com"</f>
+        <v>ConsigneeTest Registered@gmail.com</v>
       </c>
       <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
-      <c r="M3" t="str">
-        <v/>
-      </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v/>
-      </c>
-      <c r="B4" t="str">
-        <v>Registered</v>
+        <f t="shared" si="1"/>
+        <v>ConsigneeTest Registered Contact Name</v>
+      </c>
+      <c r="K3">
+        <v>92</v>
+      </c>
+      <c r="L3" t="s">
+        <v>47</v>
+      </c>
+      <c r="M3">
+        <f>M2+100000</f>
+        <v>600001</v>
+      </c>
+      <c r="N3" s="3"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
       </c>
       <c r="C4" t="str">
-        <v/>
+        <f t="shared" si="1"/>
+        <v>BuyerTest Registered Address Line 1</v>
       </c>
       <c r="D4" t="str">
-        <v/>
+        <f t="shared" si="1"/>
+        <v>BuyerTest Registered Address Line 2</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <f t="shared" si="1"/>
+        <v>BuyerTest Registered City</v>
       </c>
       <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
+        <f t="shared" si="1"/>
+        <v>BuyerTest Registered State / Province</v>
+      </c>
+      <c r="G4">
+        <v>700001</v>
+      </c>
+      <c r="H4" t="s">
+        <v>41</v>
       </c>
       <c r="I4" t="str">
-        <v/>
+        <f t="shared" si="2"/>
+        <v>BuyerTest Registered@gmail.com</v>
       </c>
       <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
-      <c r="M4" t="str">
-        <v/>
-      </c>
-      <c r="N4" t="str">
-        <v/>
-      </c>
-      <c r="O4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v/>
-      </c>
-      <c r="B5" t="str">
-        <v>Registered</v>
+        <f t="shared" si="1"/>
+        <v>BuyerTest Registered Contact Name</v>
+      </c>
+      <c r="K4">
+        <v>93</v>
+      </c>
+      <c r="L4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M4">
+        <f t="shared" ref="M4:M6" si="3">M3+100000</f>
+        <v>700001</v>
+      </c>
+      <c r="N4" s="3"/>
+    </row>
+    <row r="5" spans="1:15" ht="19" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
       </c>
       <c r="C5" t="str">
-        <v/>
+        <f t="shared" si="1"/>
+        <v>Notify PartyTest Registered Address Line 1</v>
       </c>
       <c r="D5" t="str">
-        <v/>
+        <f t="shared" si="1"/>
+        <v>Notify PartyTest Registered Address Line 2</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <f t="shared" si="1"/>
+        <v>Notify PartyTest Registered City</v>
       </c>
       <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
+        <f t="shared" si="1"/>
+        <v>Notify PartyTest Registered State / Province</v>
+      </c>
+      <c r="G5">
+        <v>800001</v>
+      </c>
+      <c r="H5" t="s">
+        <v>42</v>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <f t="shared" si="2"/>
+        <v>Notify PartyTest Registered@gmail.com</v>
       </c>
       <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v/>
-      </c>
-      <c r="M5" t="str">
-        <v/>
-      </c>
-      <c r="N5" t="str">
-        <v/>
-      </c>
-      <c r="O5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v/>
-      </c>
-      <c r="B6" t="str">
-        <v>Registered</v>
+        <f t="shared" si="1"/>
+        <v>Notify PartyTest Registered Contact Name</v>
+      </c>
+      <c r="K5">
+        <v>971</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M5">
+        <f t="shared" si="3"/>
+        <v>800001</v>
+      </c>
+      <c r="N5" s="3"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <f t="shared" si="1"/>
+        <v>VendorTest Registered Address Line 1</v>
       </c>
       <c r="D6" t="str">
-        <v/>
+        <f t="shared" si="1"/>
+        <v>VendorTest Registered Address Line 2</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <f t="shared" si="1"/>
+        <v>VendorTest Registered City</v>
       </c>
       <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
+        <f t="shared" si="1"/>
+        <v>VendorTest Registered State / Province</v>
+      </c>
+      <c r="G6">
+        <v>900001</v>
+      </c>
+      <c r="H6" t="s">
+        <v>43</v>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <f t="shared" si="2"/>
+        <v>VendorTest Registered@gmail.com</v>
       </c>
       <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v/>
-      </c>
-      <c r="M6" t="str">
-        <v/>
-      </c>
-      <c r="N6" t="str">
-        <v/>
-      </c>
-      <c r="O6" t="str">
-        <v/>
+        <f t="shared" si="1"/>
+        <v>VendorTest Registered Contact Name</v>
+      </c>
+      <c r="K6">
+        <v>254</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="3"/>
+        <v>900001</v>
+      </c>
+      <c r="N6" s="3"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="str">
+        <f>$A7&amp;" "&amp; $B7&amp;" "&amp;C$1</f>
+        <v>ExporterTest Factory Address Line 1</v>
+      </c>
+      <c r="D7" t="str">
+        <f t="shared" si="1"/>
+        <v>ExporterTest Factory Address Line 2</v>
+      </c>
+      <c r="E7" t="str">
+        <f t="shared" si="1"/>
+        <v>ExporterTest Factory City</v>
+      </c>
+      <c r="F7" t="str">
+        <f t="shared" si="1"/>
+        <v>ExporterTest Factory State / Province</v>
+      </c>
+      <c r="G7">
+        <v>500002</v>
+      </c>
+      <c r="H7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" t="str">
+        <f>$A7&amp;" "&amp; $B7&amp;"@gmail.com"</f>
+        <v>ExporterTest Factory@gmail.com</v>
+      </c>
+      <c r="J7" t="str">
+        <f t="shared" si="1"/>
+        <v>ExporterTest Factory Contact Name</v>
+      </c>
+      <c r="K7">
+        <v>91</v>
+      </c>
+      <c r="L7" t="s">
+        <v>51</v>
+      </c>
+      <c r="M7">
+        <v>500001</v>
+      </c>
+      <c r="N7" s="3"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="str">
+        <f t="shared" si="1"/>
+        <v>ConsigneeTest Factory Address Line 1</v>
+      </c>
+      <c r="D8" t="str">
+        <f t="shared" si="1"/>
+        <v>ConsigneeTest Factory Address Line 2</v>
+      </c>
+      <c r="E8" t="str">
+        <f t="shared" si="1"/>
+        <v>ConsigneeTest Factory City</v>
+      </c>
+      <c r="F8" t="str">
+        <f t="shared" si="1"/>
+        <v>ConsigneeTest Factory State / Province</v>
+      </c>
+      <c r="G8">
+        <v>500002</v>
+      </c>
+      <c r="H8" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" t="str">
+        <f t="shared" si="2"/>
+        <v>ConsigneeTest Factory@gmail.com</v>
+      </c>
+      <c r="J8" t="str">
+        <f t="shared" si="1"/>
+        <v>ConsigneeTest Factory Contact Name</v>
+      </c>
+      <c r="K8">
+        <v>92</v>
+      </c>
+      <c r="L8" t="s">
+        <v>52</v>
+      </c>
+      <c r="M8">
+        <f>M7+100000</f>
+        <v>600001</v>
+      </c>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" t="str">
+        <f t="shared" si="1"/>
+        <v>BuyerTest Factory Address Line 1</v>
+      </c>
+      <c r="D9" t="str">
+        <f t="shared" si="1"/>
+        <v>BuyerTest Factory Address Line 2</v>
+      </c>
+      <c r="E9" t="str">
+        <f t="shared" si="1"/>
+        <v>BuyerTest Factory City</v>
+      </c>
+      <c r="F9" t="str">
+        <f t="shared" si="1"/>
+        <v>BuyerTest Factory State / Province</v>
+      </c>
+      <c r="G9">
+        <v>500002</v>
+      </c>
+      <c r="H9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9" t="str">
+        <f t="shared" si="2"/>
+        <v>BuyerTest Factory@gmail.com</v>
+      </c>
+      <c r="J9" t="str">
+        <f t="shared" si="1"/>
+        <v>BuyerTest Factory Contact Name</v>
+      </c>
+      <c r="K9">
+        <v>93</v>
+      </c>
+      <c r="L9" t="s">
+        <v>53</v>
+      </c>
+      <c r="M9">
+        <f t="shared" ref="M9:M11" si="4">M8+100000</f>
+        <v>700001</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" ht="19" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" t="str">
+        <f t="shared" si="1"/>
+        <v>Notify PartyTest Factory Address Line 1</v>
+      </c>
+      <c r="D10" t="str">
+        <f t="shared" si="1"/>
+        <v>Notify PartyTest Factory Address Line 2</v>
+      </c>
+      <c r="E10" t="str">
+        <f t="shared" si="1"/>
+        <v>Notify PartyTest Factory City</v>
+      </c>
+      <c r="F10" t="str">
+        <f t="shared" si="1"/>
+        <v>Notify PartyTest Factory State / Province</v>
+      </c>
+      <c r="G10">
+        <v>500002</v>
+      </c>
+      <c r="H10" t="s">
+        <v>42</v>
+      </c>
+      <c r="I10" t="str">
+        <f t="shared" si="2"/>
+        <v>Notify PartyTest Factory@gmail.com</v>
+      </c>
+      <c r="J10" t="str">
+        <f t="shared" si="1"/>
+        <v>Notify PartyTest Factory Contact Name</v>
+      </c>
+      <c r="K10">
+        <v>971</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="4"/>
+        <v>800001</v>
+      </c>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" t="str">
+        <f t="shared" si="1"/>
+        <v>VendorTest Factory Address Line 1</v>
+      </c>
+      <c r="D11" t="str">
+        <f t="shared" si="1"/>
+        <v>VendorTest Factory Address Line 2</v>
+      </c>
+      <c r="E11" t="str">
+        <f t="shared" si="1"/>
+        <v>VendorTest Factory City</v>
+      </c>
+      <c r="F11" t="str">
+        <f t="shared" si="1"/>
+        <v>VendorTest Factory State / Province</v>
+      </c>
+      <c r="G11">
+        <v>500002</v>
+      </c>
+      <c r="H11" t="s">
+        <v>43</v>
+      </c>
+      <c r="I11" t="str">
+        <f t="shared" si="2"/>
+        <v>VendorTest Factory@gmail.com</v>
+      </c>
+      <c r="J11" t="str">
+        <f t="shared" si="1"/>
+        <v>VendorTest Factory Contact Name</v>
+      </c>
+      <c r="K11">
+        <v>254</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="4"/>
+        <v>900001</v>
+      </c>
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" t="str">
+        <f>$A12&amp;" "&amp; $B12&amp;" "&amp;C$1</f>
+        <v>ExporterTest Corporate Office Address Line 1</v>
+      </c>
+      <c r="D12" t="str">
+        <f t="shared" si="1"/>
+        <v>ExporterTest Corporate Office Address Line 2</v>
+      </c>
+      <c r="E12" t="str">
+        <f t="shared" si="1"/>
+        <v>ExporterTest Corporate Office City</v>
+      </c>
+      <c r="F12" t="str">
+        <f t="shared" si="1"/>
+        <v>ExporterTest Corporate Office State / Province</v>
+      </c>
+      <c r="G12">
+        <v>500003</v>
+      </c>
+      <c r="H12" t="s">
+        <v>39</v>
+      </c>
+      <c r="I12" t="str">
+        <f>$A12&amp;" "&amp; $B12&amp;"@gmail.com"</f>
+        <v>ExporterTest Corporate Office@gmail.com</v>
+      </c>
+      <c r="J12" t="str">
+        <f t="shared" si="1"/>
+        <v>ExporterTest Corporate Office Contact Name</v>
+      </c>
+      <c r="K12">
+        <v>91</v>
+      </c>
+      <c r="L12" t="s">
+        <v>56</v>
+      </c>
+      <c r="M12">
+        <v>500001</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" t="str">
+        <f t="shared" si="1"/>
+        <v>ConsigneeTest Corporate Office Address Line 1</v>
+      </c>
+      <c r="D13" t="str">
+        <f t="shared" si="1"/>
+        <v>ConsigneeTest Corporate Office Address Line 2</v>
+      </c>
+      <c r="E13" t="str">
+        <f t="shared" si="1"/>
+        <v>ConsigneeTest Corporate Office City</v>
+      </c>
+      <c r="F13" t="str">
+        <f t="shared" si="1"/>
+        <v>ConsigneeTest Corporate Office State / Province</v>
+      </c>
+      <c r="G13">
+        <f>G12+100000</f>
+        <v>600003</v>
+      </c>
+      <c r="H13" t="s">
+        <v>40</v>
+      </c>
+      <c r="I13" t="str">
+        <f t="shared" si="2"/>
+        <v>ConsigneeTest Corporate Office@gmail.com</v>
+      </c>
+      <c r="J13" t="str">
+        <f t="shared" si="1"/>
+        <v>ConsigneeTest Corporate Office Contact Name</v>
+      </c>
+      <c r="K13">
+        <v>92</v>
+      </c>
+      <c r="L13" t="s">
+        <v>57</v>
+      </c>
+      <c r="M13">
+        <f>M12+100000</f>
+        <v>600001</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" t="str">
+        <f t="shared" si="1"/>
+        <v>BuyerTest Corporate Office Address Line 1</v>
+      </c>
+      <c r="D14" t="str">
+        <f t="shared" si="1"/>
+        <v>BuyerTest Corporate Office Address Line 2</v>
+      </c>
+      <c r="E14" t="str">
+        <f t="shared" si="1"/>
+        <v>BuyerTest Corporate Office City</v>
+      </c>
+      <c r="F14" t="str">
+        <f t="shared" si="1"/>
+        <v>BuyerTest Corporate Office State / Province</v>
+      </c>
+      <c r="G14">
+        <f t="shared" ref="G14:G16" si="5">G13+100000</f>
+        <v>700003</v>
+      </c>
+      <c r="H14" t="s">
+        <v>41</v>
+      </c>
+      <c r="I14" t="str">
+        <f t="shared" si="2"/>
+        <v>BuyerTest Corporate Office@gmail.com</v>
+      </c>
+      <c r="J14" t="str">
+        <f t="shared" si="1"/>
+        <v>BuyerTest Corporate Office Contact Name</v>
+      </c>
+      <c r="K14">
+        <v>93</v>
+      </c>
+      <c r="L14" t="s">
+        <v>58</v>
+      </c>
+      <c r="M14">
+        <f t="shared" ref="M14:M16" si="6">M13+100000</f>
+        <v>700001</v>
+      </c>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" ht="19" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" t="str">
+        <f t="shared" si="1"/>
+        <v>Notify PartyTest Corporate Office Address Line 1</v>
+      </c>
+      <c r="D15" t="str">
+        <f t="shared" si="1"/>
+        <v>Notify PartyTest Corporate Office Address Line 2</v>
+      </c>
+      <c r="E15" t="str">
+        <f t="shared" si="1"/>
+        <v>Notify PartyTest Corporate Office City</v>
+      </c>
+      <c r="F15" t="str">
+        <f t="shared" si="1"/>
+        <v>Notify PartyTest Corporate Office State / Province</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="5"/>
+        <v>800003</v>
+      </c>
+      <c r="H15" t="s">
+        <v>42</v>
+      </c>
+      <c r="I15" t="str">
+        <f t="shared" si="2"/>
+        <v>Notify PartyTest Corporate Office@gmail.com</v>
+      </c>
+      <c r="J15" t="str">
+        <f t="shared" si="1"/>
+        <v>Notify PartyTest Corporate Office Contact Name</v>
+      </c>
+      <c r="K15">
+        <v>971</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="6"/>
+        <v>800001</v>
+      </c>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" t="str">
+        <f t="shared" si="1"/>
+        <v>VendorTest Corporate Office Address Line 1</v>
+      </c>
+      <c r="D16" t="str">
+        <f t="shared" si="1"/>
+        <v>VendorTest Corporate Office Address Line 2</v>
+      </c>
+      <c r="E16" t="str">
+        <f t="shared" si="1"/>
+        <v>VendorTest Corporate Office City</v>
+      </c>
+      <c r="F16" t="str">
+        <f t="shared" si="1"/>
+        <v>VendorTest Corporate Office State / Province</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="5"/>
+        <v>900003</v>
+      </c>
+      <c r="H16" t="s">
+        <v>43</v>
+      </c>
+      <c r="I16" t="str">
+        <f t="shared" si="2"/>
+        <v>VendorTest Corporate Office@gmail.com</v>
+      </c>
+      <c r="J16" t="str">
+        <f t="shared" si="1"/>
+        <v>VendorTest Corporate Office Contact Name</v>
+      </c>
+      <c r="K16">
+        <v>254</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="6"/>
+        <v>900001</v>
+      </c>
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="2:13" ht="19" x14ac:dyDescent="0.25">
+      <c r="M17" s="1"/>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M18" s="2"/>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="L6" r:id="rId1" display="https://www.linkmobility.com/blog/list-of-international-telephone-country-codes" xr:uid="{393D65AA-459F-F341-B776-CC668AAE0EEC}"/>
+    <hyperlink ref="L11" r:id="rId2" display="https://www.linkmobility.com/blog/list-of-international-telephone-country-codes" xr:uid="{C193FF0C-46C2-7A48-ABC8-B756C3DDC6A3}"/>
+    <hyperlink ref="L16" r:id="rId3" display="https://www.linkmobility.com/blog/list-of-international-telephone-country-codes" xr:uid="{3A55DDD6-3EE7-6C45-BC00-93F9B97FC7B1}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O6"/>
+    <ignoredError sqref="A1:O1 B3:B6 B2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>How to use this file</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>1. "Organisations" sheet — one row per organisation. Fill in the Organisation Name column for each of the 5 pre-listed types (leave Organisation Type as-is).</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>2. "Addresses" sheet — one row per address. The Organisation Name here must be typed EXACTLY the same as the matching row in the Organisations sheet (copy-paste it to be safe).</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>3. Every organisation needs at least one address. To add more addresses to the same organisation, add another row in the Addresses sheet with the same Organisation Name.</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>4. Address Type must be one of: Registered, Factory, Corporate Office, Delivery.</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v xml:space="preserve">   - Only ONE Registered / Factory / Corporate Office address is allowed per organisation.</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v xml:space="preserve">   - You CAN add multiple Delivery addresses for the same organisation.</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>5. Country must be typed exactly as it appears in the app (e.g. "India", "United States") — it is used to search a dropdown.</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>6. Phone Dial Code can be left blank — the app auto-fills it based on the Country you pick, unless you want a different one.</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>7. Required fields (per address): Address Type, Address Line 1, City, Country. Everything else is optional.</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>When you are done, save this file and hand it back — the automated script reads it directly by these exact sheet names and column order, so please don't rename sheets, reorder columns, or add extra columns.</v>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A13"/>
+    <ignoredError sqref="A1:A6 A8:A13" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>